--- a/Syllabus/CS 401R-4 F26 Schedule.xlsx
+++ b/Syllabus/CS 401R-4 F26 Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scott1/Documents/Vault/Efforts/Projects/Active/CS_401R_2026/Syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2ABB0D13-F443-4C40-BF35-B22D607AD955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178BE0B0-7769-9E48-A19A-AE2F6CAC90B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35940" yWindow="-60" windowWidth="31580" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>Sep</t>
   </si>
   <si>
-    <t>Sep 19, 2026</t>
-  </si>
-  <si>
     <t>AI Systems Development Lifecycle (AISDLC)</t>
   </si>
   <si>
@@ -441,6 +438,9 @@
   </si>
   <si>
     <t>Reading*</t>
+  </si>
+  <si>
+    <t>Sep 12, 2026</t>
   </si>
 </sst>
 </file>
@@ -466,20 +466,24 @@
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1206,10 +1210,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="81" customFormat="1" ht="20" x14ac:dyDescent="0.25">
@@ -1232,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3" s="79" t="s">
         <v>6</v>
@@ -1258,20 +1262,20 @@
         <v>3</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
@@ -1288,13 +1292,13 @@
         <v>8</v>
       </c>
       <c r="E5" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
@@ -1314,13 +1318,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
@@ -1340,13 +1344,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
@@ -1366,19 +1370,19 @@
         <v>17</v>
       </c>
       <c r="E8" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="37" t="s">
         <v>20</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>21</v>
       </c>
       <c r="J8" s="8"/>
     </row>
@@ -1396,13 +1400,13 @@
         <v>22</v>
       </c>
       <c r="E9" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
@@ -1422,13 +1426,13 @@
         <v>24</v>
       </c>
       <c r="E10" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
@@ -1448,13 +1452,13 @@
         <v>29</v>
       </c>
       <c r="E11" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="H11" s="24"/>
       <c r="I11" s="24"/>
@@ -1468,25 +1472,25 @@
         <v>5</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="66">
         <v>1</v>
       </c>
       <c r="E12" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="G12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="I12" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>36</v>
       </c>
       <c r="J12" s="10"/>
     </row>
@@ -1498,19 +1502,19 @@
         <v>6</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="67">
         <v>6</v>
       </c>
       <c r="E13" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
@@ -1524,19 +1528,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" s="67">
         <v>8</v>
       </c>
       <c r="E14" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
@@ -1550,19 +1554,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="68">
         <v>13</v>
       </c>
       <c r="E15" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
@@ -1576,28 +1580,28 @@
         <v>7</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="68">
         <v>15</v>
       </c>
       <c r="E16" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="H16" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="J16" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="70" customHeight="1" x14ac:dyDescent="0.2">
@@ -1608,28 +1612,28 @@
         <v>8</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="69">
         <v>20</v>
       </c>
       <c r="E17" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="H17" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I17" s="45">
         <v>46318</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
@@ -1640,19 +1644,19 @@
         <v>8</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="69">
         <v>22</v>
       </c>
       <c r="E18" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="G18" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
@@ -1666,19 +1670,19 @@
         <v>9</v>
       </c>
       <c r="C19" s="70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="70">
         <v>27</v>
       </c>
       <c r="E19" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="G19" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="28"/>
@@ -1692,25 +1696,25 @@
         <v>9</v>
       </c>
       <c r="C20" s="70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="70">
         <v>29</v>
       </c>
       <c r="E20" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="G20" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="H20" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="I20" s="40" t="s">
         <v>62</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>63</v>
       </c>
       <c r="J20" s="14"/>
     </row>
@@ -1722,19 +1726,19 @@
         <v>10</v>
       </c>
       <c r="C21" s="71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="71">
         <v>3</v>
       </c>
       <c r="E21" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="G21" s="15" t="s">
         <v>66</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>67</v>
       </c>
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
@@ -1748,19 +1752,19 @@
         <v>10</v>
       </c>
       <c r="C22" s="71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="71">
         <v>5</v>
       </c>
       <c r="E22" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="G22" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="H22" s="29"/>
       <c r="I22" s="29"/>
@@ -1774,19 +1778,19 @@
         <v>11</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="72">
         <v>10</v>
       </c>
       <c r="E23" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="G23" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>73</v>
       </c>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -1800,25 +1804,25 @@
         <v>11</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="72">
         <v>12</v>
       </c>
       <c r="E24" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="G24" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="H24" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="I24" s="41" t="s">
         <v>77</v>
-      </c>
-      <c r="I24" s="41" t="s">
-        <v>78</v>
       </c>
       <c r="J24" s="16"/>
     </row>
@@ -1830,19 +1834,19 @@
         <v>12</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="73">
         <v>17</v>
       </c>
       <c r="E25" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="G25" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
@@ -1856,28 +1860,28 @@
         <v>12</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="73">
         <v>19</v>
       </c>
       <c r="E26" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="H26" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="I26" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="I26" s="42" t="s">
+      <c r="J26" s="17" t="s">
         <v>86</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.2">
@@ -1888,41 +1892,41 @@
         <v>13</v>
       </c>
       <c r="C27" s="74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="74">
         <v>24</v>
       </c>
       <c r="E27" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="G27" s="18" t="s">
         <v>89</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>90</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="32"/>
       <c r="J27" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" s="75">
         <v>13</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" s="75">
         <v>26</v>
       </c>
       <c r="E28" s="61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
@@ -1938,24 +1942,24 @@
         <v>14</v>
       </c>
       <c r="C29" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="62">
         <v>1</v>
       </c>
       <c r="E29" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
       <c r="J29" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -1966,19 +1970,19 @@
         <v>14</v>
       </c>
       <c r="C30" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D30" s="62">
         <v>3</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
@@ -1992,16 +1996,16 @@
         <v>15</v>
       </c>
       <c r="C31" s="63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="63">
         <v>8</v>
       </c>
       <c r="E31" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="21"/>
@@ -2016,22 +2020,22 @@
         <v>15</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="63">
         <v>10</v>
       </c>
       <c r="E32" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="21"/>
       <c r="I32" s="21"/>
       <c r="J32" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="38" x14ac:dyDescent="0.2">
@@ -2042,26 +2046,26 @@
         <v>16</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" s="64">
         <v>16</v>
       </c>
       <c r="E33" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="I33" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="I33" s="37" t="s">
+      <c r="J33" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2082,18 +2086,18 @@
   <sheetData>
     <row r="1" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
@@ -2122,13 +2126,13 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
@@ -2157,13 +2161,13 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -2192,13 +2196,13 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
@@ -2227,13 +2231,13 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
@@ -2262,13 +2266,13 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -2297,13 +2301,13 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
